--- a/DesignTable/Data/Table/Tables/monster_deploy.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_deploy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B73AFE59-6B4E-47F1-B479-AA4DF004AA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B255D06E-EBB0-49E1-B0CE-323C3BBE5AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="0" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{13C1E156-C84A-42CE-93DB-E3F6045E3C81}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{13C1E156-C84A-42CE-93DB-E3F6045E3C81}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="21">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mon_fieldType</t>
   </si>
   <si>
@@ -98,6 +94,14 @@
   </si>
   <si>
     <t>mon_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -155,7 +159,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -170,7 +178,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="monster_deploy">
         <xsd:complexType>
@@ -185,6 +193,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -202,7 +211,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -211,13 +220,13 @@
   <autoFilter ref="A1:C2" xr:uid="{FC05C215-CA4C-4352-90CE-140FFD955AA7}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{489B8294-7FF5-4793-826B-8248D7B34F53}" uniqueName="mon_fieldType" name="mon_fieldType">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{A44A8609-9207-47EF-999E-64FAE8D62841}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{A95C7977-4804-4914-9BBA-0A1634FE704D}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -225,35 +234,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{81AC9A38-55DE-4CF5-B440-8A894B797006}" name="표1" displayName="표1" ref="A1:I4" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I4" xr:uid="{81AC9A38-55DE-4CF5-B440-8A894B797006}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{81AC9A38-55DE-4CF5-B440-8A894B797006}" name="표1" displayName="표1" ref="A1:J4" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J4" xr:uid="{81AC9A38-55DE-4CF5-B440-8A894B797006}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3567379E-4167-4719-B526-7942558E2EE9}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F155254A-F226-4011-9C44-2C3FD72EB7ED}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{42DBB27F-5BAE-42B5-8600-614EF1AF2003}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{A306EA63-F2C9-4535-B3A3-3366DFFAB869}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7AEF145E-E226-4A55-BCD7-A0564006FA94}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB419236-8491-4D4D-948C-EBE84F2A2621}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{79BC581A-00F5-4497-8907-6A4A7B5BB965}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{513BC796-CC49-4AEB-AE59-0DBFA6132096}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{5A3EF25B-8909-4CBB-B875-04629B1E95A1}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{5A3EF25B-8909-4CBB-B875-04629B1E95A1}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{1CEE02A1-338C-4B40-B386-452D08B5FE57}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -562,13 +574,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -587,10 +599,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756AB875-7C07-486B-B344-E30BE9F6176D}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,93 +628,105 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1019</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
         <v>1019</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
         <v>1019</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/monster_deploy.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_deploy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B255D06E-EBB0-49E1-B0CE-323C3BBE5AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C290A93A-60CA-42A9-80E0-F1157058DDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{13C1E156-C84A-42CE-93DB-E3F6045E3C81}"/>
   </bookViews>
@@ -211,7 +211,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -220,13 +220,13 @@
   <autoFilter ref="A1:C2" xr:uid="{FC05C215-CA4C-4352-90CE-140FFD955AA7}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{489B8294-7FF5-4793-826B-8248D7B34F53}" uniqueName="mon_fieldType" name="mon_fieldType">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{A44A8609-9207-47EF-999E-64FAE8D62841}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{A95C7977-4804-4914-9BBA-0A1634FE704D}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -238,34 +238,34 @@
   <autoFilter ref="A1:J4" xr:uid="{81AC9A38-55DE-4CF5-B440-8A894B797006}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3567379E-4167-4719-B526-7942558E2EE9}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F155254A-F226-4011-9C44-2C3FD72EB7ED}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{42DBB27F-5BAE-42B5-8600-614EF1AF2003}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{A306EA63-F2C9-4535-B3A3-3366DFFAB869}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7AEF145E-E226-4A55-BCD7-A0564006FA94}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB419236-8491-4D4D-948C-EBE84F2A2621}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{79BC581A-00F5-4497-8907-6A4A7B5BB965}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{513BC796-CC49-4AEB-AE59-0DBFA6132096}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5A3EF25B-8909-4CBB-B875-04629B1E95A1}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{1CEE02A1-338C-4B40-B386-452D08B5FE57}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/monster_deploy.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_deploy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C290A93A-60CA-42A9-80E0-F1157058DDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF8094D7-934E-457D-9ECF-6BC729E485FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{13C1E156-C84A-42CE-93DB-E3F6045E3C81}"/>
   </bookViews>
@@ -211,7 +211,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -220,13 +220,13 @@
   <autoFilter ref="A1:C2" xr:uid="{FC05C215-CA4C-4352-90CE-140FFD955AA7}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{489B8294-7FF5-4793-826B-8248D7B34F53}" uniqueName="mon_fieldType" name="mon_fieldType">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{A44A8609-9207-47EF-999E-64FAE8D62841}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{A95C7977-4804-4914-9BBA-0A1634FE704D}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -238,34 +238,34 @@
   <autoFilter ref="A1:J4" xr:uid="{81AC9A38-55DE-4CF5-B440-8A894B797006}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3567379E-4167-4719-B526-7942558E2EE9}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F155254A-F226-4011-9C44-2C3FD72EB7ED}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{42DBB27F-5BAE-42B5-8600-614EF1AF2003}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{A306EA63-F2C9-4535-B3A3-3366DFFAB869}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7AEF145E-E226-4A55-BCD7-A0564006FA94}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB419236-8491-4D4D-948C-EBE84F2A2621}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{79BC581A-00F5-4497-8907-6A4A7B5BB965}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{513BC796-CC49-4AEB-AE59-0DBFA6132096}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5A3EF25B-8909-4CBB-B875-04629B1E95A1}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{1CEE02A1-338C-4B40-B386-452D08B5FE57}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/monster_deploy.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_deploy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF8094D7-934E-457D-9ECF-6BC729E485FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C90B4AC-8BE2-4E3A-B234-6D06207CF003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{13C1E156-C84A-42CE-93DB-E3F6045E3C81}"/>
   </bookViews>
@@ -211,7 +211,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="monster_deploy_맵" RootElement="monster_deploy" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -220,13 +220,13 @@
   <autoFilter ref="A1:C2" xr:uid="{FC05C215-CA4C-4352-90CE-140FFD955AA7}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{489B8294-7FF5-4793-826B-8248D7B34F53}" uniqueName="mon_fieldType" name="mon_fieldType">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/record/mon_fieldType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{A44A8609-9207-47EF-999E-64FAE8D62841}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{A95C7977-4804-4914-9BBA-0A1634FE704D}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/record/mon_type" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -238,34 +238,34 @@
   <autoFilter ref="A1:J4" xr:uid="{81AC9A38-55DE-4CF5-B440-8A894B797006}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3567379E-4167-4719-B526-7942558E2EE9}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F155254A-F226-4011-9C44-2C3FD72EB7ED}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{42DBB27F-5BAE-42B5-8600-614EF1AF2003}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{A306EA63-F2C9-4535-B3A3-3366DFFAB869}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7AEF145E-E226-4A55-BCD7-A0564006FA94}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB419236-8491-4D4D-948C-EBE84F2A2621}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{79BC581A-00F5-4497-8907-6A4A7B5BB965}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{513BC796-CC49-4AEB-AE59-0DBFA6132096}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5A3EF25B-8909-4CBB-B875-04629B1E95A1}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{1CEE02A1-338C-4B40-B386-452D08B5FE57}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_deploy/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
